--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK28"/>
+  <dimension ref="A1:AR27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col width="12.21875" customWidth="1" min="3" max="4"/>
@@ -507,6 +507,17 @@
     <col width="17.33203125" customWidth="1" min="31" max="31"/>
     <col width="14.33203125" customWidth="1" min="32" max="32"/>
     <col width="13.109375" customWidth="1" min="33" max="33"/>
+    <col width="24.44140625" customWidth="1" min="34" max="34"/>
+    <col width="24.44140625" customWidth="1" min="35" max="35"/>
+    <col width="24.44140625" customWidth="1" min="36" max="36"/>
+    <col width="24.44140625" customWidth="1" min="37" max="37"/>
+    <col width="24.44140625" customWidth="1" min="38" max="38"/>
+    <col width="24.44140625" customWidth="1" min="39" max="39"/>
+    <col width="24.44140625" customWidth="1" min="40" max="40"/>
+    <col width="24.44140625" customWidth="1" min="41" max="41"/>
+    <col width="24.44140625" customWidth="1" min="42" max="42"/>
+    <col width="24.44140625" customWidth="1" min="43" max="43"/>
+    <col width="24.44140625" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2" customHeight="1">
@@ -615,10 +626,16 @@
           <t>Stacking</t>
         </is>
       </c>
-      <c r="AH1" s="9" t="n"/>
-      <c r="AI1" s="9" t="n"/>
-      <c r="AJ1" s="9" t="n"/>
-      <c r="AK1" s="9" t="n"/>
+      <c r="AH1" s="9" t="inlineStr">
+        <is>
+          <t>RuntimeV1TargetPolicy</t>
+        </is>
+      </c>
+      <c r="AL1" s="9" t="inlineStr">
+        <is>
+          <t>RuntimeV1Evaluator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
@@ -726,10 +743,16 @@
           <t>Stacking?</t>
         </is>
       </c>
-      <c r="AH2" s="9" t="n"/>
-      <c r="AI2" s="9" t="n"/>
-      <c r="AJ2" s="9" t="n"/>
-      <c r="AK2" s="9" t="n"/>
+      <c r="AH2" s="9" t="inlineStr">
+        <is>
+          <t>RuntimeV1TargetPolicy?</t>
+        </is>
+      </c>
+      <c r="AL2" s="9" t="inlineStr">
+        <is>
+          <t>RuntimeV1Evaluator?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -895,6 +918,61 @@
       <c r="AG3" s="9" t="inlineStr">
         <is>
           <t>溢出触发GE</t>
+        </is>
+      </c>
+      <c r="AH3" s="9" t="inlineStr">
+        <is>
+          <t>Logical target</t>
+        </is>
+      </c>
+      <c r="AI3" s="9" t="inlineStr">
+        <is>
+          <t>Avatar binding</t>
+        </is>
+      </c>
+      <c r="AJ3" s="9" t="inlineStr">
+        <is>
+          <t>Spatial binding</t>
+        </is>
+      </c>
+      <c r="AK3" s="9" t="inlineStr">
+        <is>
+          <t>Life policy</t>
+        </is>
+      </c>
+      <c r="AL3" s="9" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="AM3" s="9" t="inlineStr">
+        <is>
+          <t>Attribute set</t>
+        </is>
+      </c>
+      <c r="AN3" s="9" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="AO3" s="9" t="inlineStr">
+        <is>
+          <t>Base value</t>
+        </is>
+      </c>
+      <c r="AP3" s="9" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="AQ3" s="9" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="AR3" s="9" t="inlineStr">
+        <is>
+          <t>Maximum</t>
         </is>
       </c>
     </row>
@@ -943,6 +1021,17 @@
       </c>
       <c r="X4" s="9" t="n"/>
       <c r="Y4" s="9" t="n"/>
+      <c r="AH4" s="9" t="n"/>
+      <c r="AI4" s="9" t="n"/>
+      <c r="AJ4" s="9" t="n"/>
+      <c r="AK4" s="9" t="n"/>
+      <c r="AL4" s="9" t="n"/>
+      <c r="AM4" s="9" t="n"/>
+      <c r="AN4" s="9" t="n"/>
+      <c r="AO4" s="9" t="n"/>
+      <c r="AP4" s="9" t="n"/>
+      <c r="AQ4" s="9" t="n"/>
+      <c r="AR4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n"/>
@@ -1349,6 +1438,26 @@
           <t>9301</t>
         </is>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="n">
@@ -1374,6 +1483,26 @@
           <t>9301</t>
         </is>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="n">
@@ -1389,19 +1518,53 @@
           <t>AutoChess execute command marker</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M18" t="b">
-        <v>0</v>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>9301</t>
         </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>TargetMissingHealth</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>9001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -1425,7 +1588,6 @@
     <row r="23">
       <c r="B23" s="9" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="9" t="n"/>
     </row>
@@ -1458,23 +1620,26 @@
       <c r="N27" t="n">
         <v>2</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>9204</t>
-        </is>
+      <c r="O27" t="n">
+        <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>9001;1;0.0;3</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>9301</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>9203</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -1483,13 +1648,13 @@
         <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -1501,39 +1666,61 @@
           <t>False</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="9" t="n">
-        <v>9204</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>AutoChessPoisonTickDamage</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>AutoChess poison period tick health damage</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>9001;1;1.0;3</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>9301</t>
-        </is>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>FrozenAsc</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>RequireSameAvatar</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>AliveOnly</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>SourceAttackStackCount</t>
+        </is>
+      </c>
+      <c r="AM27" t="n">
+        <v>9001</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
+    <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="K2:M2"/>
+    <mergeCell ref="AL2:AR2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Y2:AG2"/>
     <mergeCell ref="Y1:AG1"/>
+    <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="AL1:AR1"/>
     <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
